--- a/data/trans_camb/P1413-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1413-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>4,72</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,08</t>
+          <t>15,05</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,22</t>
+          <t>10,06</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,52; -0,06</t>
+          <t>-7,19; 0,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,52; -2,75</t>
+          <t>-9,33; -2,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 8,89</t>
+          <t>0,48; 8,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,75; 8,9</t>
+          <t>0,4; 8,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 2,68</t>
+          <t>-5,02; 2,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,17; 18,83</t>
+          <t>11,16; 18,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,39</t>
+          <t>-2,21; 3,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,21; -0,83</t>
+          <t>-5,89; -0,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,75; 13,14</t>
+          <t>7,12; 12,42</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>65,13%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,34; 0,36</t>
+          <t>-42,95; 1,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-56,64; -20,03</t>
+          <t>-54,78; -19,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 70,03</t>
+          <t>1,81; 63,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,79; 63,2</t>
+          <t>1,54; 61,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,84; 19,07</t>
+          <t>-27,64; 18,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,42; 136,26</t>
+          <t>61,83; 139,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 25,36</t>
+          <t>-13,12; 22,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,84; -5,74</t>
+          <t>-35,1; -4,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45,66; 96,14</t>
+          <t>43,27; 89,9</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>3,24</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,56</t>
+          <t>12,38</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,17</t>
+          <t>7,88</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,28; -0,11</t>
+          <t>-6,05; 0,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,76; -3,0</t>
+          <t>-8,41; -2,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 4,36</t>
+          <t>-0,03; 6,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 1,41</t>
+          <t>-5,79; 1,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,57; -2,73</t>
+          <t>-9,59; -2,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,98; 16,18</t>
+          <t>8,86; 16,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; -0,17</t>
+          <t>-4,9; -0,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,03; -3,54</t>
+          <t>-8,2; -3,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 8,9</t>
+          <t>5,31; 10,28</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-1,01%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>47,45%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,91; -0,05</t>
+          <t>-39,91; 0,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,1; -24,67</t>
+          <t>-56,18; -22,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,63; 34,55</t>
+          <t>-0,22; 55,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,92; 7,96</t>
+          <t>-27,24; 9,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,49; -15,71</t>
+          <t>-44,42; -14,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,67; 91,41</t>
+          <t>40,55; 90,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,3; -1,0</t>
+          <t>-27,6; -1,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,42; -23,07</t>
+          <t>-45,99; -22,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 55,59</t>
+          <t>28,92; 67,72</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,11</t>
+          <t>6,31</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11,78</t>
+          <t>3,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,71; -10,22</t>
+          <t>-17,51; -10,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,14; -10,07</t>
+          <t>-17,41; -10,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 4,31</t>
+          <t>-4,75; 4,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,25; -7,33</t>
+          <t>-15,41; -6,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,79; -11,81</t>
+          <t>-19,69; -11,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,51; 51,08</t>
+          <t>2,33; 11,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,41; -9,77</t>
+          <t>-15,12; -9,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-17,37; -11,89</t>
+          <t>-17,38; -11,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 33,42</t>
+          <t>0,09; 6,65</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-1,32%</t>
+          <t>-0,71%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-77,45; -55,62</t>
+          <t>-77,52; -56,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,65; -55,78</t>
+          <t>-77,1; -56,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 23,93</t>
+          <t>-20,69; 24,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-56,39; -30,19</t>
+          <t>-54,35; -29,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-68,04; -48,04</t>
+          <t>-68,81; -48,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,04; 208,7</t>
+          <t>7,8; 48,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-61,69; -44,6</t>
+          <t>-60,68; -44,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-69,61; -54,78</t>
+          <t>-69,43; -54,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,59; 149,16</t>
+          <t>0,37; 31,21</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,08</t>
+          <t>1,53</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,49</t>
+          <t>11,12</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,08</t>
+          <t>6,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,13; -6,17</t>
+          <t>-12,19; -6,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,1; -4,91</t>
+          <t>-10,73; -4,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 5,52</t>
+          <t>-1,92; 4,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 6,6</t>
+          <t>-0,25; 6,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 3,02</t>
+          <t>-3,41; 3,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,56; 13,44</t>
+          <t>8,01; 14,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,8; -0,37</t>
+          <t>-4,94; -0,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,9; -1,46</t>
+          <t>-5,81; -1,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,08; 8,7</t>
+          <t>4,27; 9,12</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-64,5; -39,56</t>
+          <t>-64,53; -39,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-58,69; -31,48</t>
+          <t>-57,1; -30,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 34,67</t>
+          <t>-10,7; 30,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 44,4</t>
+          <t>-1,52; 42,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,4; 21,56</t>
+          <t>-19,33; 23,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,36; 93,72</t>
+          <t>44,74; 98,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-27,66; -2,6</t>
+          <t>-27,99; -3,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-33,4; -9,5</t>
+          <t>-33,62; -10,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18,32; 56,21</t>
+          <t>23,67; 58,86</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>2,37</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,49</t>
+          <t>11,36</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,08</t>
+          <t>7,01</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,71; -5,55</t>
+          <t>-8,84; -5,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,64; -6,39</t>
+          <t>-9,61; -6,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 3,4</t>
+          <t>0,52; 4,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,81</t>
+          <t>-3,05; 0,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -3,41</t>
+          <t>-7,09; -3,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,94; 26,69</t>
+          <t>9,58; 13,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,32; -2,85</t>
+          <t>-5,29; -2,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,85; -5,49</t>
+          <t>-7,82; -5,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,97; 16,52</t>
+          <t>5,81; 8,32</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-51,11; -36,07</t>
+          <t>-52,04; -36,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,39; -41,7</t>
+          <t>-56,26; -42,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 21,62</t>
+          <t>3,08; 26,22</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 4,43</t>
+          <t>-14,68; 4,46</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-34,69; -18,42</t>
+          <t>-35,43; -18,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,32; 142,82</t>
+          <t>46,85; 72,72</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-28,95; -16,5</t>
+          <t>-28,83; -16,82</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-42,67; -31,74</t>
+          <t>-42,67; -31,72</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>27,29; 92,86</t>
+          <t>31,45; 49,22</t>
         </is>
       </c>
     </row>
